--- a/Lista de chequeo.xlsx
+++ b/Lista de chequeo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Documents\Proyecto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Downloads\CDL-Proyecto-2ndo-trimestre\CDL-Proyecto-2ndo-trimestre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BB7048C-D9BB-49A8-99B8-0BF6A0AB7F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB9F91B-E5C6-4313-939E-BEED7C2B57FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
   <si>
     <t>Lista de Chequeo</t>
   </si>
@@ -96,17 +96,44 @@
     <t>se identifica que el objetivo no concuerda con el producto que se debe realizar</t>
   </si>
   <si>
-    <t>el levantamiento de datos fue muy debil por ende no hay rf y rnf</t>
-  </si>
-  <si>
     <t>NOTAS</t>
+  </si>
+  <si>
+    <t>Trimestre 3</t>
+  </si>
+  <si>
+    <t>En el proyecto evidencia la construcción de la base de datos usando sentencias DDL (SQL) o Schema Validation (MongoDB)</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el uso de la base de datos a través de sentencias DML (SQL), revisando existencia de datos de prueba insertados, Joins, consultas y subconsultas o MongoDB CRUD Operations y aggregations.</t>
+  </si>
+  <si>
+    <t>Dentro del esquema de seguridad de la Base de Datos se observa que el password o contraseñas contemplan encriptación de datos. Igualmente se evidencia la práctica de seguridad a los datos.</t>
+  </si>
+  <si>
+    <t>Se evidencia en el proyecto la realización del Front-End funcional (codificación), utilizando frameworks como Bootstrap, Materialize, Angular, Vue.js o React, de acuerdo con el diseño establecido en el prototipo y la base de datos. En caso de no contar con un backend desarrollado, este debe ser simulado mediante herramientas como JSON Server u otras similares. Asimismo, se debe implementar una simulación de autenticación utilizando JWT, almacenado en localStorage o sessionStorage.</t>
+  </si>
+  <si>
+    <t>Elaborar el prototipo navegable del software (HTML - CSS)</t>
+  </si>
+  <si>
+    <t>*esta es la ficha tecnica</t>
+  </si>
+  <si>
+    <t>Los mockups actuales estan desactualizados de como el proyecto esta ahora</t>
+  </si>
+  <si>
+    <t>correciones a los salarios son necesitados</t>
+  </si>
+  <si>
+    <t>aunque la normalizacion ya esta hecha y verificada no tenemos el modelo relacional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,6 +209,17 @@
       <color theme="0"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
     </font>
   </fonts>
   <fills count="4">
@@ -327,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -339,15 +377,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -360,9 +389,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -390,14 +416,42 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -416,6 +470,65 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -463,77 +576,6 @@
       </border>
     </dxf>
     <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="top" wrapText="1"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -561,24 +603,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -595,12 +619,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E16" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
-  <autoFilter ref="B2:E16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E22" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
+  <autoFilter ref="B2:E22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lista de Chequeo" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="0"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="1"/>
     <tableColumn id="4" xr3:uid="{BEB37B81-24E7-4E20-9B6C-0105A79B3860}" name="NOTAS" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -865,19 +889,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" style="19" customWidth="1"/>
-    <col min="3" max="3" width="70.140625" customWidth="1"/>
-    <col min="4" max="4" width="16.140625" style="21" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="15" customWidth="1"/>
+    <col min="3" max="3" width="78.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="17" customWidth="1"/>
     <col min="5" max="5" width="72" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="11" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -886,206 +910,285 @@
     </row>
     <row r="2" spans="1:10" ht="23.25" customHeight="1">
       <c r="A2" s="3"/>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="6" t="s">
-        <v>22</v>
+      <c r="E2" s="23" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" customHeight="1">
       <c r="A3" s="3"/>
-      <c r="B3" s="17" t="s">
+      <c r="B3" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="9"/>
+      <c r="E3" s="6" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="4" spans="1:10" ht="56.25" customHeight="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="9"/>
+      <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:10" ht="51.75" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E5" s="9" t="s">
-        <v>21</v>
-      </c>
+      <c r="D5" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E5" s="6"/>
     </row>
     <row r="6" spans="1:10" ht="55.5" customHeight="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="6" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="54" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="17" t="s">
+      <c r="B7" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="19" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="E7" s="9"/>
+        <v>9</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="51" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="17" t="s">
+      <c r="B8" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="9"/>
+      <c r="E8" s="6"/>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="89.25" customHeight="1">
       <c r="A9" s="3"/>
-      <c r="B9" s="17" t="s">
+      <c r="B9" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="9"/>
+      <c r="E9" s="6" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="53.25" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="17" t="s">
+      <c r="B10" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="E10" s="9"/>
+      <c r="D10" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E10" s="6"/>
     </row>
     <row r="11" spans="1:10" ht="48" customHeight="1">
       <c r="A11" s="3"/>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="20" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="9"/>
+      <c r="D11" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E11" s="6"/>
     </row>
     <row r="12" spans="1:10" ht="48" customHeight="1">
       <c r="A12" s="3"/>
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="9"/>
+      <c r="E12" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="48" customHeight="1">
       <c r="A13" s="3"/>
-      <c r="B13" s="17" t="s">
+      <c r="B13" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="E13" s="9"/>
+      <c r="D13" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E13" s="6"/>
     </row>
     <row r="14" spans="1:10" ht="42.75" customHeight="1">
       <c r="A14" s="3"/>
-      <c r="B14" s="17" t="s">
+      <c r="B14" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="11" t="s">
+      <c r="D14" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="9"/>
+      <c r="E14" s="6"/>
     </row>
     <row r="15" spans="1:10" ht="45.75" customHeight="1">
       <c r="A15" s="3"/>
-      <c r="B15" s="17" t="s">
+      <c r="B15" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="D15" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="9"/>
+      <c r="E15" s="6"/>
     </row>
     <row r="16" spans="1:10" ht="46.5" customHeight="1">
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="12" t="s">
+      <c r="C16" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E16" s="10"/>
+    </row>
+    <row r="17" spans="2:5" ht="52.5">
+      <c r="B17" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="D17" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="14"/>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="2:5" ht="52.5">
+      <c r="B18" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E18" s="18"/>
+    </row>
+    <row r="19" spans="2:5" ht="52.5">
+      <c r="B19" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="18"/>
+    </row>
+    <row r="20" spans="2:5" ht="110.25">
+      <c r="B20" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E20" s="18"/>
+    </row>
+    <row r="21" spans="2:5" ht="45.75">
+      <c r="B21" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="18"/>
+    </row>
+    <row r="22" spans="2:5" ht="52.5">
+      <c r="B22" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="18"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <tableParts count="1">

--- a/Lista de chequeo.xlsx
+++ b/Lista de chequeo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\felip\Downloads\CDL-Proyecto-2ndo-trimestre\CDL-Proyecto-2ndo-trimestre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Documents\Proyecto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FB9F91B-E5C6-4313-939E-BEED7C2B57FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BB7048C-D9BB-49A8-99B8-0BF6A0AB7F54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="23">
   <si>
     <t>Lista de Chequeo</t>
   </si>
@@ -96,44 +96,17 @@
     <t>se identifica que el objetivo no concuerda con el producto que se debe realizar</t>
   </si>
   <si>
+    <t>el levantamiento de datos fue muy debil por ende no hay rf y rnf</t>
+  </si>
+  <si>
     <t>NOTAS</t>
-  </si>
-  <si>
-    <t>Trimestre 3</t>
-  </si>
-  <si>
-    <t>En el proyecto evidencia la construcción de la base de datos usando sentencias DDL (SQL) o Schema Validation (MongoDB)</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia el uso de la base de datos a través de sentencias DML (SQL), revisando existencia de datos de prueba insertados, Joins, consultas y subconsultas o MongoDB CRUD Operations y aggregations.</t>
-  </si>
-  <si>
-    <t>Dentro del esquema de seguridad de la Base de Datos se observa que el password o contraseñas contemplan encriptación de datos. Igualmente se evidencia la práctica de seguridad a los datos.</t>
-  </si>
-  <si>
-    <t>Se evidencia en el proyecto la realización del Front-End funcional (codificación), utilizando frameworks como Bootstrap, Materialize, Angular, Vue.js o React, de acuerdo con el diseño establecido en el prototipo y la base de datos. En caso de no contar con un backend desarrollado, este debe ser simulado mediante herramientas como JSON Server u otras similares. Asimismo, se debe implementar una simulación de autenticación utilizando JWT, almacenado en localStorage o sessionStorage.</t>
-  </si>
-  <si>
-    <t>Elaborar el prototipo navegable del software (HTML - CSS)</t>
-  </si>
-  <si>
-    <t>*esta es la ficha tecnica</t>
-  </si>
-  <si>
-    <t>Los mockups actuales estan desactualizados de como el proyecto esta ahora</t>
-  </si>
-  <si>
-    <t>correciones a los salarios son necesitados</t>
-  </si>
-  <si>
-    <t>aunque la normalizacion ya esta hecha y verificada no tenemos el modelo relacional</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -210,17 +183,6 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
-    <font>
-      <sz val="8"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -365,7 +327,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -377,6 +339,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -389,6 +360,9 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -416,42 +390,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="8">
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -470,65 +416,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="0"/>
-        <name val="Times New Roman"/>
-        <family val="1"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -576,6 +463,77 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="top" wrapText="1"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <top style="thin">
           <color indexed="64"/>
@@ -603,6 +561,24 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -619,12 +595,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E22" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="7" tableBorderDxfId="6" totalsRowBorderDxfId="5">
-  <autoFilter ref="B2:E22" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E16" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
+  <autoFilter ref="B2:E16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="4"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="1"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lista de Chequeo" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="0"/>
     <tableColumn id="4" xr3:uid="{BEB37B81-24E7-4E20-9B6C-0105A79B3860}" name="NOTAS" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -889,19 +865,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="78.42578125" customWidth="1"/>
-    <col min="4" max="4" width="15.28515625" style="17" customWidth="1"/>
+    <col min="2" max="2" width="18.85546875" style="19" customWidth="1"/>
+    <col min="3" max="3" width="70.140625" customWidth="1"/>
+    <col min="4" max="4" width="16.140625" style="21" customWidth="1"/>
     <col min="5" max="5" width="72" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1">
       <c r="A1" s="1"/>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
@@ -910,285 +886,206 @@
     </row>
     <row r="2" spans="1:10" ht="23.25" customHeight="1">
       <c r="A2" s="3"/>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="D2" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>21</v>
+      <c r="E2" s="6" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" customHeight="1">
       <c r="A3" s="3"/>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>28</v>
-      </c>
+      <c r="E3" s="9"/>
     </row>
     <row r="4" spans="1:10" ht="56.25" customHeight="1">
       <c r="A4" s="3"/>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="6"/>
+      <c r="E4" s="9"/>
     </row>
     <row r="5" spans="1:10" ht="51.75" customHeight="1">
       <c r="A5" s="3"/>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E5" s="6"/>
+      <c r="D5" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="55.5" customHeight="1">
       <c r="A6" s="3"/>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="9" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="54" customHeight="1">
       <c r="A7" s="3"/>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>29</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="E7" s="9"/>
     </row>
     <row r="8" spans="1:10" ht="51" customHeight="1">
       <c r="A8" s="3"/>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="6"/>
+      <c r="E8" s="9"/>
       <c r="J8" s="4"/>
     </row>
     <row r="9" spans="1:10" ht="89.25" customHeight="1">
       <c r="A9" s="3"/>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>30</v>
-      </c>
+      <c r="E9" s="9"/>
     </row>
     <row r="10" spans="1:10" ht="53.25" customHeight="1">
       <c r="A10" s="3"/>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E10" s="6"/>
+      <c r="D10" s="10" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="9"/>
     </row>
     <row r="11" spans="1:10" ht="48" customHeight="1">
       <c r="A11" s="3"/>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E11" s="6"/>
+      <c r="D11" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E11" s="9"/>
     </row>
     <row r="12" spans="1:10" ht="48" customHeight="1">
       <c r="A12" s="3"/>
-      <c r="B12" s="13" t="s">
+      <c r="B12" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>31</v>
-      </c>
+      <c r="E12" s="9"/>
     </row>
     <row r="13" spans="1:10" ht="48" customHeight="1">
       <c r="A13" s="3"/>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E13" s="6"/>
+      <c r="D13" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="9"/>
     </row>
     <row r="14" spans="1:10" ht="42.75" customHeight="1">
       <c r="A14" s="3"/>
-      <c r="B14" s="13" t="s">
+      <c r="B14" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="8" t="s">
+      <c r="D14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="6"/>
+      <c r="E14" s="9"/>
     </row>
     <row r="15" spans="1:10" ht="45.75" customHeight="1">
       <c r="A15" s="3"/>
-      <c r="B15" s="13" t="s">
+      <c r="B15" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="8" t="s">
+      <c r="D15" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E15" s="6"/>
+      <c r="E15" s="9"/>
     </row>
     <row r="16" spans="1:10" ht="46.5" customHeight="1">
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E16" s="10"/>
-    </row>
-    <row r="17" spans="2:5" ht="52.5">
-      <c r="B17" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>23</v>
-      </c>
-      <c r="D17" s="9" t="s">
+      <c r="D16" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18" spans="2:5" ht="52.5">
-      <c r="B18" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E18" s="18"/>
-    </row>
-    <row r="19" spans="2:5" ht="52.5">
-      <c r="B19" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="2:5" ht="110.25">
-      <c r="B20" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>26</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E20" s="18"/>
-    </row>
-    <row r="21" spans="2:5" ht="45.75">
-      <c r="B21" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="18"/>
-    </row>
-    <row r="22" spans="2:5" ht="52.5">
-      <c r="B22" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E22" s="18"/>
+      <c r="E16" s="14"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <tableParts count="1">

--- a/Lista de chequeo.xlsx
+++ b/Lista de chequeo.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="8280"/>
+    <workbookView windowWidth="22188" windowHeight="9000"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="29">
   <si>
     <t>Lista de Chequeo</t>
   </si>
@@ -50,9 +50,6 @@
     <t>✔</t>
   </si>
   <si>
-    <t>*esta es la ficha tecnica</t>
-  </si>
-  <si>
     <t>En el proyecto se evidencian la elaboración del mapa de procesos que implica el sistema de información (BPMN del proceso de negocio, no del aplicativo a desarrollar)</t>
   </si>
   <si>
@@ -62,61 +59,49 @@
     <t>En el proyecto se evidencian los requerimientos funcionales y no funcionales usando el estándar IEEE Std 830-1998, IEEE 1233-1998, IEEE 29148:2018 o historias de usuario (Scrum)</t>
   </si>
   <si>
+    <t>En el proyecto se evidencia validación de requerimientos (Realización de un prototipo usando mockups o wireframes)</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el uso de sistemas de control de versiones (Opcional)</t>
+  </si>
+  <si>
+    <t>SEGUNDO TRIMESTRE</t>
+  </si>
+  <si>
+    <t>Trimestre 2</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencian formatos de fichas técnicas, estimación de costos de software-hardware, análisis comparativo de proveedores considerando costos, cantidad y especificaciones técnicas de acuerdo con las características de la solución de software y las necesidades de la empresa.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el diagrama de casos de uso y documentación de casos de uso (formato de casos de uso extendido) de acuerdo con el refinamiento de requisitos.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el modelo entidad relación notación crows foot</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia la normalización del modelo relaciónal, identificando las 3FN</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el diccionario de datos</t>
+  </si>
+  <si>
+    <t>Se evidencia el diagrama de clases del proyecto donde se ven las clases y relaciones usando el estándar UML 2.4.1 o superior</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia la realización del diagrama de despliegue usando el estándar UML 2.4.1 o superior</t>
+  </si>
+  <si>
+    <t>TERCER TRIMESTRE</t>
+  </si>
+  <si>
+    <t>Trimestre 3</t>
+  </si>
+  <si>
+    <t>En el proyecto evidencia la construcción de la base de datos usando sentencias DDL (SQL) o Schema Validation (MongoDB)</t>
+  </si>
+  <si>
     <t>X</t>
-  </si>
-  <si>
-    <t>se identifica que el objetivo no concuerda con el producto que se debe realizar</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia validación de requerimientos (Realización de un prototipo usando mockups o wireframes)</t>
-  </si>
-  <si>
-    <t>Los mockups actuales estan desactualizados de como el proyecto esta ahora</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia el uso de sistemas de control de versiones (Opcional)</t>
-  </si>
-  <si>
-    <t>SEGUNDO TRIMESTRE</t>
-  </si>
-  <si>
-    <t>Trimestre 2</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencian formatos de fichas técnicas, estimación de costos de software-hardware, análisis comparativo de proveedores considerando costos, cantidad y especificaciones técnicas de acuerdo con las características de la solución de software y las necesidades de la empresa.</t>
-  </si>
-  <si>
-    <t>correciones a los salarios son necesitados</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia el diagrama de casos de uso y documentación de casos de uso (formato de casos de uso extendido) de acuerdo con el refinamiento de requisitos.</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia el modelo entidad relación notación crows foot</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia la normalización del modelo relaciónal, identificando las 3FN</t>
-  </si>
-  <si>
-    <t>aunque la normalizacion ya esta hecha y verificada no tenemos el modelo relacional</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia el diccionario de datos</t>
-  </si>
-  <si>
-    <t>Se evidencia el diagrama de clases del proyecto donde se ven las clases y relaciones usando el estándar UML 2.4.1 o superior</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia la realización del diagrama de despliegue usando el estándar UML 2.4.1 o superior</t>
-  </si>
-  <si>
-    <t>TERCER TRIMESTRE</t>
-  </si>
-  <si>
-    <t>Trimestre 3</t>
-  </si>
-  <si>
-    <t>En el proyecto evidencia la construcción de la base de datos usando sentencias DDL (SQL) o Schema Validation (MongoDB)</t>
   </si>
   <si>
     <t>En el proyecto se evidencia el uso de la base de datos a través de sentencias DML (SQL), revisando existencia de datos de prueba insertados, Joins, consultas y subconsultas o MongoDB CRUD Operations y aggregations.</t>
@@ -141,7 +126,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="32">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -165,35 +150,15 @@
     </font>
     <font>
       <b/>
-      <i/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="36"/>
       <color theme="0"/>
       <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="36"/>
-      <color theme="0"/>
-      <name val="Segoe UI Black"/>
       <charset val="134"/>
     </font>
     <font>
@@ -211,20 +176,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="0"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -687,7 +638,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -700,7 +651,7 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -980,137 +931,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1136,121 +1087,100 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1732,292 +1662,282 @@
       <c r="C2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="9" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" ht="60" customHeight="1" spans="1:5">
       <c r="A3" s="6"/>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>7</v>
-      </c>
+      <c r="E3" s="13"/>
     </row>
     <row r="4" ht="56.25" customHeight="1" spans="1:5">
       <c r="A4" s="6"/>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="13" t="s">
+      <c r="C4" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="14"/>
+      <c r="E4" s="13"/>
     </row>
     <row r="5" ht="51.75" customHeight="1" spans="1:5">
       <c r="A5" s="6"/>
-      <c r="B5" s="11" t="s">
+      <c r="B5" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="13" t="s">
+      <c r="C5" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E5" s="14"/>
+      <c r="E5" s="13"/>
     </row>
     <row r="6" ht="55.5" customHeight="1" spans="1:5">
       <c r="A6" s="6"/>
-      <c r="B6" s="11" t="s">
+      <c r="B6" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>12</v>
-      </c>
+      <c r="C6" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="13"/>
     </row>
     <row r="7" ht="54" customHeight="1" spans="1:5">
       <c r="A7" s="6"/>
-      <c r="B7" s="11" t="s">
+      <c r="B7" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>14</v>
-      </c>
+      <c r="C7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="13"/>
     </row>
     <row r="8" ht="51" customHeight="1" spans="1:10">
       <c r="A8" s="6"/>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="17" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="18" t="s">
+      <c r="C8" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E8" s="19"/>
-      <c r="J8" s="47"/>
+      <c r="E8" s="17"/>
+      <c r="J8" s="40"/>
     </row>
     <row r="9" ht="89.25" customHeight="1" spans="1:5">
-      <c r="A9" s="20"/>
-      <c r="B9" s="21"/>
-      <c r="C9" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="23"/>
-      <c r="E9" s="24"/>
+      <c r="A9" s="18"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D9" s="21"/>
+      <c r="E9" s="22"/>
     </row>
     <row r="10" ht="68" customHeight="1" spans="1:5">
       <c r="A10" s="6"/>
-      <c r="B10" s="25" t="s">
-        <v>17</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="28" t="s">
-        <v>19</v>
-      </c>
+      <c r="B10" s="23" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="25"/>
     </row>
     <row r="11" ht="48" customHeight="1" spans="1:5">
       <c r="A11" s="6"/>
-      <c r="B11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D11" s="13" t="s">
+      <c r="B11" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="14"/>
+      <c r="E11" s="13"/>
     </row>
     <row r="12" ht="48" customHeight="1" spans="1:5">
       <c r="A12" s="6"/>
-      <c r="B12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="13" t="s">
+      <c r="B12" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="14"/>
+      <c r="E12" s="13"/>
     </row>
     <row r="13" ht="48" customHeight="1" spans="1:5">
       <c r="A13" s="6"/>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="14" t="s">
-        <v>23</v>
-      </c>
+      <c r="D13" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="13"/>
     </row>
     <row r="14" ht="42.75" customHeight="1" spans="1:5">
       <c r="A14" s="6"/>
-      <c r="B14" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" s="13" t="s">
+      <c r="B14" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="D14" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="14"/>
+      <c r="E14" s="13"/>
     </row>
     <row r="15" ht="45.75" customHeight="1" spans="1:5">
       <c r="A15" s="6"/>
-      <c r="B15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="12" t="s">
+      <c r="B15" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" ht="46.5" customHeight="1" spans="2:5">
+      <c r="B16" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" ht="46.95" spans="2:5">
+      <c r="B17" s="26" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="28" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="29"/>
+    </row>
+    <row r="18" ht="52.95" spans="2:5">
+      <c r="B18" s="30"/>
+      <c r="C18" s="31" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+    </row>
+    <row r="19" ht="52.2" spans="2:5">
+      <c r="B19" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="E19" s="37"/>
+    </row>
+    <row r="20" ht="52.2" spans="2:5">
+      <c r="B20" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D20" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="13"/>
+    </row>
+    <row r="21" ht="52.2" spans="2:5">
+      <c r="B21" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E21" s="13"/>
+    </row>
+    <row r="22" ht="109.2" spans="2:5">
+      <c r="B22" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="38" t="s">
+        <v>24</v>
+      </c>
+      <c r="E22" s="13"/>
+    </row>
+    <row r="23" ht="46.2" spans="2:5">
+      <c r="B23" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="13"/>
+    </row>
+    <row r="24" ht="52.95" spans="2:5">
+      <c r="B24" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="E15" s="14"/>
-    </row>
-    <row r="16" ht="46.5" customHeight="1" spans="2:5">
-      <c r="B16" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="14"/>
-    </row>
-    <row r="17" ht="46.95" spans="2:5">
-      <c r="B17" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="D17" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="33"/>
-    </row>
-    <row r="18" ht="52.95" spans="2:5">
-      <c r="B18" s="34"/>
-      <c r="C18" s="35" t="s">
-        <v>27</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="37"/>
-    </row>
-    <row r="19" ht="52.2" spans="2:5">
-      <c r="B19" s="38" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="41"/>
-    </row>
-    <row r="20" ht="52.2" spans="2:5">
-      <c r="B20" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C20" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="43"/>
-    </row>
-    <row r="21" ht="52.2" spans="2:5">
-      <c r="B21" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C21" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="D21" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="43"/>
-    </row>
-    <row r="22" ht="109.2" spans="2:5">
-      <c r="B22" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C22" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="D22" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="43"/>
-    </row>
-    <row r="23" ht="46.2" spans="2:5">
-      <c r="B23" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="C23" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="43"/>
-    </row>
-    <row r="24" ht="52.95" spans="2:5">
-      <c r="B24" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="45" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="46"/>
+      <c r="D24" s="39" t="s">
+        <v>24</v>
+      </c>
+      <c r="E24" s="29"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Lista de chequeo.xlsx
+++ b/Lista de chequeo.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Downloads\CDL-Proyecto-4to-trimestre\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4283ABE4-683F-4013-B692-52A540EF316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="22188" windowHeight="9000"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -18,8 +24,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
   <si>
     <t>Lista de Chequeo</t>
   </si>
@@ -114,19 +118,25 @@
   </si>
   <si>
     <t>Elaborar el prototipo navegable del software (HTML - CSS)</t>
+  </si>
+  <si>
+    <t>cambiar el alcance del proyecto (Es mas sobre todo lo que va a ser el proyecto a futuro osease a donde va)</t>
+  </si>
+  <si>
+    <t>actualizar en base al proyecto mas nuevo</t>
+  </si>
+  <si>
+    <t>cambiar los rnf y rf y Agregar inferfaz grafica a la parte: Requerimientos No Funcionales (RNF)</t>
+  </si>
+  <si>
+    <t>actualizar en base al proyecto mas nuevo (En la tabla paquete toca colocar los productos y servicios)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="42" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;_);_(@_)"/>
-    <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="27">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -182,152 +192,8 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="36">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -352,194 +218,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="29">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -815,253 +495,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1114,9 +552,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1182,81 +617,25 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Coma" xfId="1" builtinId="3"/>
-    <cellStyle name="Moneda" xfId="2" builtinId="4"/>
-    <cellStyle name="Porcentaje" xfId="3" builtinId="5"/>
-    <cellStyle name="Coma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Moneda [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Hipervínculo" xfId="6" builtinId="8"/>
-    <cellStyle name="Hipervínculo visitado" xfId="7" builtinId="9"/>
-    <cellStyle name="Nota" xfId="8" builtinId="10"/>
-    <cellStyle name="Texto de advertencia" xfId="9" builtinId="11"/>
-    <cellStyle name="Título" xfId="10" builtinId="15"/>
-    <cellStyle name="Texto explicativo" xfId="11" builtinId="53"/>
-    <cellStyle name="Título 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Título 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Título 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Título 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Entrada" xfId="16" builtinId="20"/>
-    <cellStyle name="Salida" xfId="17" builtinId="21"/>
-    <cellStyle name="Cálculo" xfId="18" builtinId="22"/>
-    <cellStyle name="Celda de comprobación" xfId="19" builtinId="23"/>
-    <cellStyle name="Celda vinculada" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Correcto" xfId="22" builtinId="26"/>
-    <cellStyle name="Incorrecto" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutro" xfId="24" builtinId="28"/>
-    <cellStyle name="Énfasis1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Énfasis1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Énfasis1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Énfasis1" xfId="28" builtinId="32"/>
-    <cellStyle name="Énfasis2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Énfasis2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Énfasis2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Énfasis2" xfId="32" builtinId="36"/>
-    <cellStyle name="Énfasis3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Énfasis3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Énfasis3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Énfasis3" xfId="36" builtinId="40"/>
-    <cellStyle name="Énfasis4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Énfasis4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Énfasis4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Énfasis4" xfId="40" builtinId="44"/>
-    <cellStyle name="Énfasis5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Énfasis5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Énfasis5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Énfasis5" xfId="44" builtinId="48"/>
-    <cellStyle name="Énfasis6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Énfasis6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Énfasis6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Énfasis6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="1"/>
-        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="12"/>
         <color theme="0"/>
+        <name val="Times New Roman"/>
+        <scheme val="none"/>
       </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-      <alignment vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
       <border>
-        <left/>
-        <right style="thin">
+        <left style="thin">
           <color auto="1"/>
-        </right>
+        </left>
+        <right/>
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -1267,48 +646,15 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
-        <b val="1"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <u val="none"/>
-        <sz val="12"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor theme="2" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
-        <family val="1"/>
         <b val="0"/>
         <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="36"/>
         <color theme="0"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
       <fill>
         <patternFill patternType="solid">
@@ -1333,19 +679,60 @@
     </dxf>
     <dxf>
       <font>
-        <name val="Times New Roman"/>
-        <scheme val="none"/>
+        <b/>
+        <i val="0"/>
         <strike val="0"/>
         <u val="none"/>
         <sz val="12"/>
         <color theme="0"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
       </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <border>
         <left style="thin">
           <color auto="1"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="12"/>
+        <color theme="0"/>
+        <name val="Times New Roman"/>
+        <family val="1"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-0.499984740745262"/>
+        </patternFill>
+      </fill>
+      <alignment vertical="center" wrapText="1"/>
+      <border>
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -1360,18 +747,21 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
   </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="B2:E24" totalsRowShown="0">
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="B2:E24" etc:filterBottomFollowUsedRange="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E24" totalsRowShown="0">
+  <autoFilter ref="B2:E24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" name="Trimestre" dataDxfId="0"/>
-    <tableColumn id="2" name="Lista de Chequeo" dataDxfId="1"/>
-    <tableColumn id="3" name="Entregables" dataDxfId="2"/>
-    <tableColumn id="4" name="NOTAS" dataDxfId="3"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lista de Chequeo" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="NOTAS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1629,23 +1019,24 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J24"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="11.4259259259259" customWidth="1"/>
-    <col min="2" max="2" width="15.4259259259259" style="1" customWidth="1"/>
-    <col min="3" max="3" width="78.4259259259259" customWidth="1"/>
-    <col min="4" max="4" width="15.287037037037" style="2" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="78.42578125" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="72" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="19.5" customHeight="1" spans="1:3">
+    <row r="1" spans="1:10" ht="19.5" customHeight="1">
       <c r="A1" s="3"/>
       <c r="B1" s="4" t="s">
         <v>0</v>
@@ -1654,7 +1045,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" ht="23.25" customHeight="1" spans="1:5">
+    <row r="2" spans="1:10" ht="23.25" customHeight="1">
       <c r="A2" s="6"/>
       <c r="B2" s="7" t="s">
         <v>2</v>
@@ -1669,7 +1060,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" ht="60" customHeight="1" spans="1:5">
+    <row r="3" spans="1:10" ht="60" customHeight="1">
       <c r="A3" s="6"/>
       <c r="B3" s="10" t="s">
         <v>4</v>
@@ -1680,9 +1071,11 @@
       <c r="D3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="13"/>
-    </row>
-    <row r="4" ht="56.25" customHeight="1" spans="1:5">
+      <c r="E3" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="56.25" customHeight="1">
       <c r="A4" s="6"/>
       <c r="B4" s="10" t="s">
         <v>4</v>
@@ -1695,7 +1088,7 @@
       </c>
       <c r="E4" s="13"/>
     </row>
-    <row r="5" ht="51.75" customHeight="1" spans="1:5">
+    <row r="5" spans="1:10" ht="51.75" customHeight="1">
       <c r="A5" s="6"/>
       <c r="B5" s="10" t="s">
         <v>4</v>
@@ -1708,7 +1101,7 @@
       </c>
       <c r="E5" s="13"/>
     </row>
-    <row r="6" ht="55.5" customHeight="1" spans="1:5">
+    <row r="6" spans="1:10" ht="55.5" customHeight="1">
       <c r="A6" s="6"/>
       <c r="B6" s="10" t="s">
         <v>4</v>
@@ -1719,9 +1112,11 @@
       <c r="D6" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="13"/>
-    </row>
-    <row r="7" ht="54" customHeight="1" spans="1:5">
+      <c r="E6" s="13" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="54" customHeight="1">
       <c r="A7" s="6"/>
       <c r="B7" s="10" t="s">
         <v>4</v>
@@ -1734,7 +1129,7 @@
       </c>
       <c r="E7" s="13"/>
     </row>
-    <row r="8" ht="51" customHeight="1" spans="1:10">
+    <row r="8" spans="1:10" ht="51" customHeight="1">
       <c r="A8" s="6"/>
       <c r="B8" s="15" t="s">
         <v>4</v>
@@ -1746,31 +1141,31 @@
         <v>6</v>
       </c>
       <c r="E8" s="17"/>
-      <c r="J8" s="40"/>
-    </row>
-    <row r="9" ht="89.25" customHeight="1" spans="1:5">
-      <c r="A9" s="18"/>
-      <c r="B9" s="19"/>
-      <c r="C9" s="20" t="s">
+      <c r="J8" s="39"/>
+    </row>
+    <row r="9" spans="1:10" ht="89.25" customHeight="1">
+      <c r="A9" s="6"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="22"/>
-    </row>
-    <row r="10" ht="68" customHeight="1" spans="1:5">
+      <c r="D9" s="20"/>
+      <c r="E9" s="21"/>
+    </row>
+    <row r="10" spans="1:10" ht="68.099999999999994" customHeight="1">
       <c r="A10" s="6"/>
-      <c r="B10" s="23" t="s">
+      <c r="B10" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C10" s="23" t="s">
         <v>14</v>
       </c>
       <c r="D10" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E10" s="25"/>
-    </row>
-    <row r="11" ht="48" customHeight="1" spans="1:5">
+      <c r="E10" s="24"/>
+    </row>
+    <row r="11" spans="1:10" ht="48" customHeight="1">
       <c r="A11" s="6"/>
       <c r="B11" s="10" t="s">
         <v>13</v>
@@ -1781,9 +1176,11 @@
       <c r="D11" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E11" s="13"/>
-    </row>
-    <row r="12" ht="48" customHeight="1" spans="1:5">
+      <c r="E11" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="48" customHeight="1">
       <c r="A12" s="6"/>
       <c r="B12" s="10" t="s">
         <v>13</v>
@@ -1794,9 +1191,11 @@
       <c r="D12" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E12" s="13"/>
-    </row>
-    <row r="13" ht="48" customHeight="1" spans="1:5">
+      <c r="E12" s="13" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="48" customHeight="1">
       <c r="A13" s="6"/>
       <c r="B13" s="10" t="s">
         <v>13</v>
@@ -1807,9 +1206,11 @@
       <c r="D13" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="13"/>
-    </row>
-    <row r="14" ht="42.75" customHeight="1" spans="1:5">
+      <c r="E13" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="42.75" customHeight="1">
       <c r="A14" s="6"/>
       <c r="B14" s="10" t="s">
         <v>13</v>
@@ -1820,9 +1221,11 @@
       <c r="D14" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E14" s="13"/>
-    </row>
-    <row r="15" ht="45.75" customHeight="1" spans="1:5">
+      <c r="E14" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="45.75" customHeight="1">
       <c r="A15" s="6"/>
       <c r="B15" s="10" t="s">
         <v>13</v>
@@ -1833,9 +1236,11 @@
       <c r="D15" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="E15" s="13"/>
-    </row>
-    <row r="16" ht="46.5" customHeight="1" spans="2:5">
+      <c r="E15" s="13" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="46.5" customHeight="1">
       <c r="B16" s="10" t="s">
         <v>13</v>
       </c>
@@ -1847,75 +1252,75 @@
       </c>
       <c r="E16" s="13"/>
     </row>
-    <row r="17" ht="46.95" spans="2:5">
-      <c r="B17" s="26" t="s">
+    <row r="17" spans="2:5" ht="45.75">
+      <c r="B17" s="25" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D17" s="28" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="29"/>
-    </row>
-    <row r="18" ht="52.95" spans="2:5">
-      <c r="B18" s="30"/>
-      <c r="C18" s="31" t="s">
+      <c r="D17" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="28"/>
+    </row>
+    <row r="18" spans="2:5" ht="52.5">
+      <c r="B18" s="29"/>
+      <c r="C18" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-    </row>
-    <row r="19" ht="52.2" spans="2:5">
-      <c r="B19" s="34" t="s">
+      <c r="D18" s="31"/>
+      <c r="E18" s="32"/>
+    </row>
+    <row r="19" spans="2:5" ht="52.5">
+      <c r="B19" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="D19" s="36" t="s">
+      <c r="D19" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="E19" s="37"/>
-    </row>
-    <row r="20" ht="52.2" spans="2:5">
+      <c r="E19" s="36"/>
+    </row>
+    <row r="20" spans="2:5" ht="52.5">
       <c r="B20" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C20" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="37" t="s">
         <v>24</v>
       </c>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" ht="52.2" spans="2:5">
+    <row r="21" spans="2:5" ht="52.5">
       <c r="B21" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C21" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D21" s="38" t="s">
+      <c r="D21" s="37" t="s">
         <v>24</v>
       </c>
       <c r="E21" s="13"/>
     </row>
-    <row r="22" ht="109.2" spans="2:5">
+    <row r="22" spans="2:5" ht="110.25">
       <c r="B22" s="15" t="s">
         <v>22</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D22" s="38" t="s">
+      <c r="D22" s="37" t="s">
         <v>24</v>
       </c>
       <c r="E22" s="13"/>
     </row>
-    <row r="23" ht="46.2" spans="2:5">
+    <row r="23" spans="2:5" ht="45.75">
       <c r="B23" s="15" t="s">
         <v>22</v>
       </c>
@@ -1927,22 +1332,21 @@
       </c>
       <c r="E23" s="13"/>
     </row>
-    <row r="24" ht="52.95" spans="2:5">
-      <c r="B24" s="26" t="s">
+    <row r="24" spans="2:5" ht="52.5">
+      <c r="B24" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="27" t="s">
+      <c r="C24" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="D24" s="39" t="s">
+      <c r="D24" s="38" t="s">
         <v>24</v>
       </c>
-      <c r="E24" s="29"/>
+      <c r="E24" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-  <headerFooter/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>

--- a/Lista de chequeo.xlsx
+++ b/Lista de chequeo.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Downloads\CDL-Proyecto-4to-trimestre\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Downloads\CDL-Proyecto-6to-trimestre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4283ABE4-683F-4013-B692-52A540EF316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB62382-91C6-491A-A20E-E956DBB94056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="48">
   <si>
     <t>Lista de Chequeo</t>
   </si>
@@ -120,23 +120,68 @@
     <t>Elaborar el prototipo navegable del software (HTML - CSS)</t>
   </si>
   <si>
-    <t>cambiar el alcance del proyecto (Es mas sobre todo lo que va a ser el proyecto a futuro osease a donde va)</t>
-  </si>
-  <si>
-    <t>actualizar en base al proyecto mas nuevo</t>
-  </si>
-  <si>
-    <t>cambiar los rnf y rf y Agregar inferfaz grafica a la parte: Requerimientos No Funcionales (RNF)</t>
-  </si>
-  <si>
-    <t>actualizar en base al proyecto mas nuevo (En la tabla paquete toca colocar los productos y servicios)</t>
+    <t>CUARTO TRIMESTRE</t>
+  </si>
+  <si>
+    <t>QUINTO TRIMESTRE</t>
+  </si>
+  <si>
+    <t>SEXTO TRIMESTRE</t>
+  </si>
+  <si>
+    <t>Trimestre 4</t>
+  </si>
+  <si>
+    <t>Trimestre 5</t>
+  </si>
+  <si>
+    <t>Trimestre 6</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia que se haya usado alguna técnica de pruebas de software.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia un plan de instalación, plan de respaldo, plan de migración y capacitación.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia algún modelo de calidad.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencian manuales de instalación, técnico y de usuario.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el despliegue del aplicativo según el diseño de la arquitectura en UML (Diagrama de despliegue o Diagrama de arquitectura de nube).</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el uso de sistemas de control de versiones.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el desarrollo de la codificación al 100%</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el consumo de la API Rest con aplicaciones móviles.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia la implementación de la API REST documentada (swagger u otra herramienta).</t>
+  </si>
+  <si>
+    <t>En el proyecto móvil se evidencia la aplicación de una metodología ágil. (Historias de Usuario, roles, sprints, Backlog, etc)</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia la implementación de la API REST agregando seguridad.</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia que el front end web consuma la API REST (Angular, Vue.js, react u otros), con un avance del 80% de la codificación</t>
+  </si>
+  <si>
+    <t>En el proyecto se evidencia el uso de sistemas de control de versiones.B29:E31+30:30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -172,13 +217,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="36"/>
       <color theme="0"/>
       <name val="Segoe UI Black"/>
@@ -190,6 +228,37 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Segoe UI Black"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -214,12 +283,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="1" tint="0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -228,13 +297,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color auto="1"/>
       </left>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom style="thin">
@@ -244,94 +313,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
         <color auto="1"/>
       </left>
       <right style="thin">
@@ -347,19 +328,6 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
       <right style="thin">
         <color auto="1"/>
       </right>
@@ -376,67 +344,11 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
       <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
+        <color theme="0"/>
       </bottom>
       <diagonal/>
     </border>
@@ -445,38 +357,33 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
+      <left/>
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom/>
@@ -486,20 +393,40 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
+      <right/>
+      <top style="thin">
         <color auto="1"/>
       </top>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -519,108 +446,100 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="8">
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -631,17 +550,23 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <border>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right/>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -662,19 +587,25 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center"/>
-      <border>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -695,19 +626,25 @@
         </patternFill>
       </fill>
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <border>
+      <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </left>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -728,16 +665,52 @@
         </patternFill>
       </fill>
       <alignment vertical="center" wrapText="1"/>
-      <border>
+      <border diagonalUp="0" diagonalDown="0">
         <left/>
         <right style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
         </bottom>
       </border>
     </dxf>
@@ -755,13 +728,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E24" totalsRowShown="0">
-  <autoFilter ref="B2:E24" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E40" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+  <autoFilter ref="B2:E40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="3"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lista de Chequeo" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="1"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="NOTAS" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lista de Chequeo" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="2"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="NOTAS" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1025,7 +998,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J40"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -1047,304 +1020,480 @@
     </row>
     <row r="2" spans="1:10" ht="23.25" customHeight="1">
       <c r="A2" s="6"/>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="D2" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="27" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="60" customHeight="1">
       <c r="A3" s="6"/>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>29</v>
-      </c>
+      <c r="D3" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="29"/>
     </row>
     <row r="4" spans="1:10" ht="56.25" customHeight="1">
       <c r="A4" s="6"/>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="13"/>
+      <c r="D4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="29"/>
     </row>
     <row r="5" spans="1:10" ht="51.75" customHeight="1">
       <c r="A5" s="6"/>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="13"/>
+      <c r="D5" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E5" s="29"/>
     </row>
     <row r="6" spans="1:10" ht="55.5" customHeight="1">
       <c r="A6" s="6"/>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="13" t="s">
-        <v>31</v>
-      </c>
+      <c r="D6" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="29"/>
     </row>
     <row r="7" spans="1:10" ht="54" customHeight="1">
       <c r="A7" s="6"/>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="13"/>
+      <c r="D7" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E7" s="29"/>
     </row>
     <row r="8" spans="1:10" ht="51" customHeight="1">
       <c r="A8" s="6"/>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="16" t="s">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="17"/>
-      <c r="J8" s="39"/>
-    </row>
-    <row r="9" spans="1:10" ht="89.25" customHeight="1">
+      <c r="D8" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" s="29"/>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:10" ht="42" customHeight="1">
       <c r="A9" s="6"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19" t="s">
+      <c r="B9" s="30"/>
+      <c r="C9" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="31"/>
     </row>
     <row r="10" spans="1:10" ht="68.099999999999994" customHeight="1">
       <c r="A10" s="6"/>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="24"/>
+      <c r="D10" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="29"/>
     </row>
     <row r="11" spans="1:10" ht="48" customHeight="1">
       <c r="A11" s="6"/>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="D11" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E11" s="29"/>
     </row>
     <row r="12" spans="1:10" ht="48" customHeight="1">
       <c r="A12" s="6"/>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>32</v>
-      </c>
+      <c r="D12" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="29"/>
     </row>
     <row r="13" spans="1:10" ht="48" customHeight="1">
       <c r="A13" s="6"/>
-      <c r="B13" s="10" t="s">
+      <c r="B13" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="D13" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E13" s="29"/>
     </row>
     <row r="14" spans="1:10" ht="42.75" customHeight="1">
       <c r="A14" s="6"/>
-      <c r="B14" s="10" t="s">
+      <c r="B14" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>30</v>
-      </c>
+      <c r="D14" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E14" s="29"/>
     </row>
     <row r="15" spans="1:10" ht="45.75" customHeight="1">
       <c r="A15" s="6"/>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="13" t="s">
+      <c r="D15" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="29"/>
+    </row>
+    <row r="16" spans="1:10" ht="46.5" customHeight="1">
+      <c r="B16" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="29"/>
+    </row>
+    <row r="17" spans="1:9" ht="46.5" thickBot="1">
+      <c r="B17" s="28" t="s">
+        <v>13</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="29"/>
+    </row>
+    <row r="18" spans="1:9" ht="52.5">
+      <c r="B18" s="30"/>
+      <c r="C18" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="D18" s="10"/>
+      <c r="E18" s="31"/>
+      <c r="I18" s="24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="45.75">
+      <c r="B19" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="29"/>
+      <c r="I19" s="14" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" ht="47.25">
+      <c r="B20" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="29"/>
+    </row>
+    <row r="21" spans="1:9" ht="47.25">
+      <c r="B21" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="29"/>
+    </row>
+    <row r="22" spans="1:9" ht="110.25">
+      <c r="B22" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D22" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="29"/>
+    </row>
+    <row r="23" spans="1:9" ht="45.75">
+      <c r="B23" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E23" s="29"/>
+    </row>
+    <row r="24" spans="1:9" ht="45.75">
+      <c r="B24" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="29"/>
+    </row>
+    <row r="25" spans="1:9" ht="45.75">
+      <c r="B25" s="21"/>
+      <c r="C25" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="15"/>
+    </row>
+    <row r="26" spans="1:9" ht="45.75">
+      <c r="B26" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="13" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="16"/>
+    </row>
+    <row r="27" spans="1:9" ht="45.75">
+      <c r="B27" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C27" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="16"/>
+    </row>
+    <row r="28" spans="1:9" ht="45.75">
+      <c r="B28" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C28" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="D28" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="16"/>
+    </row>
+    <row r="29" spans="1:9" ht="45.75">
+      <c r="B29" s="21"/>
+      <c r="C29" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" ht="46.5" customHeight="1">
-      <c r="B16" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="13"/>
-    </row>
-    <row r="17" spans="2:5" ht="45.75">
-      <c r="B17" s="25" t="s">
-        <v>13</v>
-      </c>
-      <c r="C17" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="28"/>
-    </row>
-    <row r="18" spans="2:5" ht="52.5">
-      <c r="B18" s="29"/>
-      <c r="C18" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-    </row>
-    <row r="19" spans="2:5" ht="52.5">
-      <c r="B19" s="33" t="s">
-        <v>22</v>
-      </c>
-      <c r="C19" s="34" t="s">
-        <v>23</v>
-      </c>
-      <c r="D19" s="35" t="s">
-        <v>24</v>
-      </c>
-      <c r="E19" s="36"/>
-    </row>
-    <row r="20" spans="2:5" ht="52.5">
-      <c r="B20" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="D20" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="13"/>
-    </row>
-    <row r="21" spans="2:5" ht="52.5">
-      <c r="B21" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E21" s="13"/>
-    </row>
-    <row r="22" spans="2:5" ht="110.25">
-      <c r="B22" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="D22" s="37" t="s">
-        <v>24</v>
-      </c>
-      <c r="E22" s="13"/>
-    </row>
-    <row r="23" spans="2:5" ht="45.75">
-      <c r="B23" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="13"/>
-    </row>
-    <row r="24" spans="2:5" ht="52.5">
-      <c r="B24" s="25" t="s">
-        <v>22</v>
-      </c>
-      <c r="C24" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="D24" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="E24" s="28"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="15"/>
+    </row>
+    <row r="30" spans="1:9" ht="45.75">
+      <c r="A30" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D30" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E30" s="16"/>
+    </row>
+    <row r="31" spans="1:9" ht="45.75">
+      <c r="B31" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C31" s="13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D31" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="16"/>
+    </row>
+    <row r="32" spans="1:9" ht="45.75">
+      <c r="B32" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D32" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="16"/>
+    </row>
+    <row r="33" spans="2:5" ht="45.75">
+      <c r="B33" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="C33" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="16"/>
+    </row>
+    <row r="34" spans="2:5" ht="45.75">
+      <c r="B34" s="21"/>
+      <c r="C34" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="22"/>
+      <c r="E34" s="15"/>
+    </row>
+    <row r="35" spans="2:5" ht="45.75">
+      <c r="B35" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C35" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D35" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E35" s="16"/>
+    </row>
+    <row r="36" spans="2:5" ht="45.75">
+      <c r="B36" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C36" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="D36" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="16"/>
+    </row>
+    <row r="37" spans="2:5" ht="45.75">
+      <c r="B37" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C37" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D37" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="16"/>
+    </row>
+    <row r="38" spans="2:5" ht="45.75">
+      <c r="B38" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C38" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D38" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E38" s="16"/>
+    </row>
+    <row r="39" spans="2:5" ht="47.25">
+      <c r="B39" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C39" s="13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D39" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="16"/>
+    </row>
+    <row r="40" spans="2:5" ht="45.75">
+      <c r="B40" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C40" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="D40" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E40" s="20"/>
     </row>
   </sheetData>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
   <tableParts count="1">

--- a/Lista de chequeo.xlsx
+++ b/Lista de chequeo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SENA\Downloads\CDL-Proyecto-6to-trimestre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCB62382-91C6-491A-A20E-E956DBB94056}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A762D419-95A7-49DD-92AD-982036A16A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="47">
   <si>
     <t>Lista de Chequeo</t>
   </si>
@@ -172,9 +172,6 @@
   </si>
   <si>
     <t>En el proyecto se evidencia que el front end web consuma la API REST (Angular, Vue.js, react u otros), con un avance del 80% de la codificación</t>
-  </si>
-  <si>
-    <t>En el proyecto se evidencia el uso de sistemas de control de versiones.B29:E31+30:30</t>
   </si>
 </sst>
 </file>
@@ -523,24 +520,6 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <font>
         <strike val="0"/>
         <u val="none"/>
@@ -692,6 +671,22 @@
       </border>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <border>
         <bottom style="thin">
           <color indexed="64"/>
@@ -706,12 +701,14 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -728,13 +725,13 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E40" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="6" tableBorderDxfId="7" totalsRowBorderDxfId="5">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Tabla1" displayName="Tabla1" ref="B2:E40" totalsRowShown="0" headerRowDxfId="7" headerRowBorderDxfId="6" tableBorderDxfId="5" totalsRowBorderDxfId="4">
   <autoFilter ref="B2:E40" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lista de Chequeo" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="2"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="NOTAS" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Trimestre" dataDxfId="3"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Lista de Chequeo" dataDxfId="2"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Entregables" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="NOTAS" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1362,9 +1359,7 @@
       <c r="E29" s="15"/>
     </row>
     <row r="30" spans="1:9" ht="45.75">
-      <c r="A30" s="23" t="s">
-        <v>47</v>
-      </c>
+      <c r="A30" s="23"/>
       <c r="B30" s="12" t="s">
         <v>33</v>
       </c>
